--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.07749674325935</v>
+        <v>9.437593220779645</v>
       </c>
       <c r="D2" t="n">
-        <v>57.88791306077476</v>
+        <v>9.406785872375899</v>
       </c>
       <c r="E2" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F2" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.01961387418299</v>
+        <v>6.665687254554736</v>
       </c>
       <c r="D3" t="n">
-        <v>40.74775153034216</v>
+        <v>6.621509623680602</v>
       </c>
       <c r="E3" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F3" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.05512291495305</v>
+        <v>6.83395747367987</v>
       </c>
       <c r="D4" t="n">
-        <v>41.83092822850103</v>
+        <v>6.797525837131418</v>
       </c>
       <c r="E4" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F4" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.69507275319934</v>
+        <v>7.587949322394893</v>
       </c>
       <c r="D5" t="n">
-        <v>46.50283490163088</v>
+        <v>7.556710671515018</v>
       </c>
       <c r="E5" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F5" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>64.2068809257612</v>
+        <v>10.43361815043619</v>
       </c>
       <c r="D6" t="n">
-        <v>64.07944372982907</v>
+        <v>10.41290960609722</v>
       </c>
       <c r="E6" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F6" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.54060315152326</v>
+        <v>6.587848012122531</v>
       </c>
       <c r="D7" t="n">
-        <v>40.25530174442169</v>
+        <v>6.541486533468524</v>
       </c>
       <c r="E7" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F7" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.73351908524954</v>
+        <v>10.68169685135305</v>
       </c>
       <c r="D8" t="n">
-        <v>65.66329657360082</v>
+        <v>10.67028569321013</v>
       </c>
       <c r="E8" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F8" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.40658840791593</v>
+        <v>5.753570616286338</v>
       </c>
       <c r="D9" t="n">
-        <v>35.14811241344544</v>
+        <v>5.711568267184884</v>
       </c>
       <c r="E9" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F9" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.66786544496399</v>
+        <v>5.796028134806648</v>
       </c>
       <c r="D10" t="n">
-        <v>35.50558477062287</v>
+        <v>5.769657525226218</v>
       </c>
       <c r="E10" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F10" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41851028780296</v>
+        <v>4.130507921767982</v>
       </c>
       <c r="D11" t="n">
-        <v>25.13209730993442</v>
+        <v>4.083965812864343</v>
       </c>
       <c r="E11" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F11" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.19341172644707</v>
+        <v>6.368929405547648</v>
       </c>
       <c r="D12" t="n">
-        <v>39.14201116540356</v>
+        <v>6.360576814378079</v>
       </c>
       <c r="E12" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F12" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.44891970942246</v>
+        <v>3.32294945278115</v>
       </c>
       <c r="D13" t="n">
-        <v>20.19111201475245</v>
+        <v>3.281055702397274</v>
       </c>
       <c r="E13" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F13" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.99325919975107</v>
+        <v>2.11140461995955</v>
       </c>
       <c r="D14" t="n">
-        <v>12.71196586793605</v>
+        <v>2.065694453539608</v>
       </c>
       <c r="E14" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F14" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.00945201276048</v>
+        <v>3.576535952073578</v>
       </c>
       <c r="D15" t="n">
-        <v>21.82620608735159</v>
+        <v>3.546758489194634</v>
       </c>
       <c r="E15" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F15" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>53.65483566802615</v>
+        <v>8.718910796054249</v>
       </c>
       <c r="D16" t="n">
-        <v>53.6839135867358</v>
+        <v>8.723635957844568</v>
       </c>
       <c r="E16" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F16" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>49.78523542925469</v>
+        <v>8.090100757253888</v>
       </c>
       <c r="D17" t="n">
-        <v>49.71638581085537</v>
+        <v>8.078912694263998</v>
       </c>
       <c r="E17" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F17" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>9.469104710720543</v>
+        <v>1.538729515492088</v>
       </c>
       <c r="D18" t="n">
-        <v>9.460840690917285</v>
+        <v>1.537386612274059</v>
       </c>
       <c r="E18" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F18" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>23.33833188976265</v>
+        <v>3.79247893208643</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47091940106998</v>
+        <v>3.814024402673871</v>
       </c>
       <c r="E19" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F19" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>42.22461176897875</v>
+        <v>6.861499412459047</v>
       </c>
       <c r="D20" t="n">
-        <v>42.21694132162696</v>
+        <v>6.860252964764381</v>
       </c>
       <c r="E20" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F20" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>36.29939805636271</v>
+        <v>5.898652184158941</v>
       </c>
       <c r="D21" t="n">
-        <v>36.43958308044093</v>
+        <v>5.921432250571652</v>
       </c>
       <c r="E21" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F21" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>15.25068365196926</v>
+        <v>2.478236093445005</v>
       </c>
       <c r="D22" t="n">
-        <v>15.508609344989</v>
+        <v>2.520149018560712</v>
       </c>
       <c r="E22" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F22" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>50.67150113717997</v>
+        <v>8.234118934791745</v>
       </c>
       <c r="D23" t="n">
-        <v>50.70041375140927</v>
+        <v>8.238817234604007</v>
       </c>
       <c r="E23" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F23" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>18.09355315205346</v>
+        <v>2.940202387208687</v>
       </c>
       <c r="D24" t="n">
-        <v>18.38144964819946</v>
+        <v>2.986985567832412</v>
       </c>
       <c r="E24" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F24" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>25.87348600154893</v>
+        <v>4.204441475251701</v>
       </c>
       <c r="D25" t="n">
-        <v>26.143281311725</v>
+        <v>4.248283213155313</v>
       </c>
       <c r="E25" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F25" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>59.79024343770529</v>
+        <v>9.715914558627109</v>
       </c>
       <c r="D26" t="n">
-        <v>59.85499533626473</v>
+        <v>9.726436742143019</v>
       </c>
       <c r="E26" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F26" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>33.55099732595637</v>
+        <v>5.452037065467911</v>
       </c>
       <c r="D27" t="n">
-        <v>33.77516126016754</v>
+        <v>5.488463704777226</v>
       </c>
       <c r="E27" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F27" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>36.33024611625354</v>
+        <v>5.9036649938912</v>
       </c>
       <c r="D28" t="n">
-        <v>36.60225247503442</v>
+        <v>5.947866027193093</v>
       </c>
       <c r="E28" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F28" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>60.33491233436907</v>
+        <v>9.804423254334974</v>
       </c>
       <c r="D29" t="n">
-        <v>60.46997392551426</v>
+        <v>9.826370762896067</v>
       </c>
       <c r="E29" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F29" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>60.99271991214863</v>
+        <v>9.911316985724152</v>
       </c>
       <c r="D30" t="n">
-        <v>61.19775879184158</v>
+        <v>9.944635803674258</v>
       </c>
       <c r="E30" t="n">
-        <v>16.0701052010218</v>
+        <v>2.611392095166043</v>
       </c>
       <c r="F30" t="n">
-        <v>16.06571630785203</v>
+        <v>2.610678900025955</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
